--- a/data_lake/industry/CFM/eMCP.xlsx
+++ b/data_lake/industry/CFM/eMCP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/CFM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2519194E-74B6-44E0-A414-011B06599281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3BD1F9-5C4A-F94B-BE6B-B5476F1C75B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18120" yWindow="780" windowWidth="17880" windowHeight="20760" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="eMCP(eMMC + LPDDR4X)64GB+32Gb" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -69,29 +69,29 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -129,42 +129,42 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -442,19 +442,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -500,7 +500,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -523,7 +523,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -546,7 +546,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -569,7 +569,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -592,7 +592,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -615,7 +615,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -638,7 +638,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -661,7 +661,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -684,7 +684,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -707,7 +707,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -730,7 +730,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -753,7 +753,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -776,7 +776,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -799,7 +799,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -822,7 +822,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -845,7 +845,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -868,7 +868,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -891,7 +891,7 @@
         <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -914,7 +914,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -937,7 +937,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -960,7 +960,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -983,7 +983,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -1190,7 +1190,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -1213,7 +1213,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -1259,7 +1259,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -1671,6 +1671,167 @@
       </c>
       <c r="G53" s="9">
         <v>83</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>82</v>
+      </c>
+      <c r="F54" s="9">
+        <v>84.7</v>
+      </c>
+      <c r="G54" s="9">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>82</v>
+      </c>
+      <c r="F55" s="9">
+        <v>84.7</v>
+      </c>
+      <c r="G55" s="9">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>81.5</v>
+      </c>
+      <c r="F56" s="9">
+        <v>84</v>
+      </c>
+      <c r="G56" s="9">
+        <v>82.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>81.5</v>
+      </c>
+      <c r="F57" s="9">
+        <v>84</v>
+      </c>
+      <c r="G57" s="9">
+        <v>82.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>81.5</v>
+      </c>
+      <c r="F58" s="9">
+        <v>84</v>
+      </c>
+      <c r="G58" s="9">
+        <v>82.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>81.5</v>
+      </c>
+      <c r="F59" s="9">
+        <v>84</v>
+      </c>
+      <c r="G59" s="9">
+        <v>82.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>81.5</v>
+      </c>
+      <c r="F60" s="9">
+        <v>84</v>
+      </c>
+      <c r="G60" s="9">
+        <v>82.5</v>
       </c>
     </row>
   </sheetData>
@@ -1682,19 +1843,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6D90D4-0805-4F1F-B873-D654865F68EF}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1717,7 +1878,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -1740,7 +1901,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -1763,7 +1924,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -1786,7 +1947,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -1809,7 +1970,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -1832,7 +1993,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -1855,7 +2016,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -1878,7 +2039,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -1901,7 +2062,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -1924,7 +2085,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -1947,7 +2108,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -1970,7 +2131,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -1993,7 +2154,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -2016,7 +2177,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -2039,7 +2200,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -2062,7 +2223,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -2085,7 +2246,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -2108,7 +2269,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -2131,7 +2292,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -2154,7 +2315,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -2177,7 +2338,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -2200,7 +2361,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -2223,7 +2384,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -2246,7 +2407,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -2269,7 +2430,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -2292,7 +2453,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2315,7 +2476,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2338,7 +2499,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2361,7 +2522,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2384,7 +2545,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -2407,7 +2568,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -2430,7 +2591,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -2453,7 +2614,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -2476,7 +2637,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -2499,7 +2660,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -2522,7 +2683,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -2545,7 +2706,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -2568,7 +2729,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -2591,7 +2752,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -2614,7 +2775,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -2637,7 +2798,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -2660,7 +2821,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -2683,7 +2844,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -2706,7 +2867,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -2729,7 +2890,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -2752,7 +2913,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -2775,7 +2936,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -2798,7 +2959,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -2821,7 +2982,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -2844,7 +3005,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -2867,7 +3028,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -2890,7 +3051,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -2910,6 +3071,167 @@
         <v>90.5</v>
       </c>
       <c r="G53" s="9">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.458333333333314</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>87.5</v>
+      </c>
+      <c r="F54" s="9">
+        <v>90.5</v>
+      </c>
+      <c r="G54" s="9">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.458333333333313</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>87.5</v>
+      </c>
+      <c r="F55" s="9">
+        <v>90.5</v>
+      </c>
+      <c r="G55" s="9">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.458333333333312</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>87.5</v>
+      </c>
+      <c r="F56" s="9">
+        <v>90.5</v>
+      </c>
+      <c r="G56" s="9">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.458333333333311</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>87.5</v>
+      </c>
+      <c r="F57" s="9">
+        <v>90.5</v>
+      </c>
+      <c r="G57" s="9">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333331</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>87.5</v>
+      </c>
+      <c r="F58" s="9">
+        <v>90.5</v>
+      </c>
+      <c r="G58" s="9">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.458333333333309</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>87.5</v>
+      </c>
+      <c r="F59" s="9">
+        <v>90.5</v>
+      </c>
+      <c r="G59" s="9">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.458333333333308</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>87.5</v>
+      </c>
+      <c r="F60" s="9">
+        <v>90.5</v>
+      </c>
+      <c r="G60" s="9">
         <v>89</v>
       </c>
     </row>
@@ -2922,20 +3244,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F328918B-C38E-4C53-9F1E-0761925FE522}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="9"/>
-    <col min="6" max="6" width="10.19921875" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2958,7 +3280,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -2981,7 +3303,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -3004,7 +3326,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -3027,7 +3349,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -3050,7 +3372,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -3073,7 +3395,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -3096,7 +3418,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -3119,7 +3441,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -3142,7 +3464,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -3165,7 +3487,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -3188,7 +3510,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -3211,7 +3533,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -3234,7 +3556,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3257,7 +3579,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3280,7 +3602,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3303,7 +3625,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3326,7 +3648,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3349,7 +3671,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3372,7 +3694,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3395,7 +3717,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3418,7 +3740,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3441,7 +3763,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3464,7 +3786,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -3487,7 +3809,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -3510,7 +3832,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -3533,7 +3855,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -3556,7 +3878,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -3579,7 +3901,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -3602,7 +3924,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -3625,7 +3947,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3648,7 +3970,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3671,7 +3993,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3694,7 +4016,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -3717,7 +4039,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -3740,7 +4062,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -3763,7 +4085,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -3786,7 +4108,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -3809,7 +4131,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -3832,7 +4154,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -3855,7 +4177,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -3878,7 +4200,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -3901,7 +4223,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -3924,7 +4246,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -3947,7 +4269,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -3970,7 +4292,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -3993,7 +4315,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -4016,7 +4338,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -4039,7 +4361,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -4062,7 +4384,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -4085,7 +4407,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -4108,7 +4430,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -4131,7 +4453,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -4152,6 +4474,167 @@
       </c>
       <c r="G53" s="9">
         <v>107</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.458333333333314</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>106.5</v>
+      </c>
+      <c r="F54" s="9">
+        <v>109</v>
+      </c>
+      <c r="G54" s="9">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.458333333333313</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>106.5</v>
+      </c>
+      <c r="F55" s="9">
+        <v>109</v>
+      </c>
+      <c r="G55" s="9">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.458333333333312</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>104.5</v>
+      </c>
+      <c r="F56" s="9">
+        <v>107</v>
+      </c>
+      <c r="G56" s="9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.458333333333311</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>104.5</v>
+      </c>
+      <c r="F57" s="9">
+        <v>107</v>
+      </c>
+      <c r="G57" s="9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333331</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>104.5</v>
+      </c>
+      <c r="F58" s="9">
+        <v>107</v>
+      </c>
+      <c r="G58" s="9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.458333333333309</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>104.5</v>
+      </c>
+      <c r="F59" s="9">
+        <v>107</v>
+      </c>
+      <c r="G59" s="9">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.458333333333308</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>104.5</v>
+      </c>
+      <c r="F60" s="9">
+        <v>107</v>
+      </c>
+      <c r="G60" s="9">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
